--- a/data/trending_integrated_20261023_14.xlsx
+++ b/data/trending_integrated_20261023_14.xlsx
@@ -563,171 +563,171 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>진양산업</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1969</v>
+        <v>5300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.43%</t>
+          <t>'+25.30%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.14</v>
+        <v>-0.76</v>
       </c>
       <c r="E2" t="n">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="H2" t="n">
-        <v>4.87</v>
+        <v>2.67</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1635</v>
+        <v>4230</v>
       </c>
       <c r="K2" t="n">
-        <v>1600</v>
+        <v>4355</v>
       </c>
       <c r="L2" t="n">
-        <v>2035</v>
+        <v>5380</v>
       </c>
       <c r="M2" t="n">
-        <v>1538</v>
+        <v>4210</v>
       </c>
       <c r="N2" t="n">
-        <v>5.01</v>
+        <v>3.43</v>
       </c>
       <c r="O2" t="n">
-        <v>72296442246</v>
+        <v>17193795714</v>
       </c>
       <c r="P2" t="n">
-        <v>4980</v>
+        <v>8020</v>
       </c>
       <c r="Q2" t="n">
-        <v>735</v>
+        <v>3660</v>
       </c>
       <c r="R2" t="n">
-        <v>-2000</v>
+        <v>-112000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 관련 사업 성장 기대 및 대기업 수혜주 언급. 단기 급등 후 매도 권유와 물량 확보 움직임 관찰.</t>
+          <t>무죄 판결 가능성에 대한 기대와 함께 물량 털어내기에 대한 언급이 있음. 법 전문가들의 의견과 대법원 관련 예상, 그리고 증거재판주의에 대한 논의가 이루어짐.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['휴머노이드', '로봇', 'CES']</t>
+          <t>['무죄', '대법원', '증거재판주의']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>003780</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59900</v>
+        <v>1945</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.12%</t>
+          <t>'+18.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.18</v>
+        <v>-0.14</v>
       </c>
       <c r="E3" t="n">
-        <v>380</v>
+        <v>135</v>
       </c>
       <c r="F3" t="n">
-        <v>201</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>1114</v>
+        <v>235</v>
       </c>
       <c r="H3" t="n">
-        <v>38.9</v>
+        <v>4.87</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>55400</v>
+        <v>1635</v>
       </c>
       <c r="K3" t="n">
-        <v>56300</v>
+        <v>1600</v>
       </c>
       <c r="L3" t="n">
-        <v>61300</v>
+        <v>2035</v>
       </c>
       <c r="M3" t="n">
-        <v>56200</v>
+        <v>1538</v>
       </c>
       <c r="N3" t="n">
-        <v>37.72</v>
+        <v>5.01</v>
       </c>
       <c r="O3" t="n">
-        <v>651834744650</v>
+        <v>73742327739</v>
       </c>
       <c r="P3" t="n">
-        <v>67300</v>
+        <v>4980</v>
       </c>
       <c r="Q3" t="n">
-        <v>23150</v>
+        <v>735</v>
       </c>
       <c r="R3" t="n">
-        <v>1522000</v>
+        <v>-2000</v>
       </c>
       <c r="S3" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인/기관의 대규모 매수 유입 및 자사주 매입/소각 공시 기반 상승 전망.</t>
+          <t>휴머노이드 로봇 관련 사업 성장 기대 및 대기업 수혜주 언급. 단기 급등 후 매도 권유와 물량 확보 움직임 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주', '매입', '공시']</t>
+          <t>['휴머노이드', '로봇', 'CES']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>진양산업</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4495</v>
+        <v>60100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.26%</t>
+          <t>'+8.48%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.76</v>
+        <v>1.18</v>
       </c>
       <c r="E4" t="n">
-        <v>91</v>
+        <v>385</v>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>205</v>
       </c>
       <c r="G4" t="n">
-        <v>138</v>
+        <v>1128</v>
       </c>
       <c r="H4" t="n">
-        <v>2.67</v>
+        <v>38.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,143 +779,143 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4230</v>
+        <v>55400</v>
       </c>
       <c r="K4" t="n">
-        <v>4355</v>
+        <v>56300</v>
       </c>
       <c r="L4" t="n">
-        <v>4820</v>
+        <v>61300</v>
       </c>
       <c r="M4" t="n">
-        <v>4210</v>
+        <v>56200</v>
       </c>
       <c r="N4" t="n">
-        <v>3.43</v>
+        <v>37.72</v>
       </c>
       <c r="O4" t="n">
-        <v>9647621663</v>
+        <v>657297642450</v>
       </c>
       <c r="P4" t="n">
-        <v>8020</v>
+        <v>67300</v>
       </c>
       <c r="Q4" t="n">
-        <v>3660</v>
+        <v>23150</v>
       </c>
       <c r="R4" t="n">
-        <v>-112000</v>
+        <v>1522000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>무죄 판결 가능성에 대한 기대와 함께 물량 털어내기에 대한 언급이 있음. 법 전문가들의 의견과 대법원 관련 예상, 그리고 증거재판주의에 대한 논의가 이루어짐.</t>
+          <t>외인/기관의 대규모 매수 유입 및 자사주 매입/소각 공시 기반 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['무죄', '대법원', '증거재판주의']</t>
+          <t>['자사주', '매입', '공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>003780</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3867</v>
+        <v>1260000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.12%</t>
+          <t>'+3.03%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>322</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>167</v>
+        <v>526</v>
       </c>
       <c r="G5" t="n">
-        <v>857</v>
+        <v>1553</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>48.77</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3750</v>
+        <v>1223000</v>
       </c>
       <c r="K5" t="n">
-        <v>3905</v>
+        <v>1200000</v>
       </c>
       <c r="L5" t="n">
-        <v>4550</v>
+        <v>1263000</v>
       </c>
       <c r="M5" t="n">
-        <v>3815</v>
+        <v>1171000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>152979799321</v>
+        <v>3246414360500</v>
       </c>
       <c r="P5" t="n">
-        <v>7050</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2500</v>
+        <v>468000</v>
       </c>
       <c r="R5" t="n">
-        <v>-251000</v>
+        <v>-405000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>166000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크 부각과 함께 방산주로서의 상승 가능성을 언급하는 게시글.</t>
+          <t>솔리다임 상장 철회 이슈를 긍정적인 호재로 인식하며, 주가 상승에 대한 기대감이 높게 나타남. 반도체 업황 개선 전망과 함께 바닥 탈출 및 강한 상승 추세 전환을 예상하는 분석이 주를 이룸.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['북한 리스크', '방산주', '김정은']</t>
+          <t>['솔리다임 상장 철회', '주가 상승 기대', '반도체 업황']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1256000</v>
+        <v>3840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.70%</t>
+          <t>'+2.40%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>335</v>
       </c>
       <c r="F6" t="n">
-        <v>527</v>
+        <v>172</v>
       </c>
       <c r="G6" t="n">
-        <v>1565</v>
+        <v>868</v>
       </c>
       <c r="H6" t="n">
-        <v>48.77</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1223000</v>
+        <v>3750</v>
       </c>
       <c r="K6" t="n">
-        <v>1200000</v>
+        <v>3905</v>
       </c>
       <c r="L6" t="n">
-        <v>1263000</v>
+        <v>4550</v>
       </c>
       <c r="M6" t="n">
-        <v>1171000</v>
+        <v>3815</v>
       </c>
       <c r="N6" t="n">
-        <v>48.79</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3183044658500</v>
+        <v>154415692119</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>7050</v>
       </c>
       <c r="Q6" t="n">
-        <v>468000</v>
+        <v>2500</v>
       </c>
       <c r="R6" t="n">
-        <v>-405000</v>
+        <v>-251000</v>
       </c>
       <c r="S6" t="n">
-        <v>166000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 호재 언급과 함께 주가 상승 기대. 외인 주도 우상향 추세 가능성 제시.</t>
+          <t>북한 관련 지정학적 리스크 부각과 함께 방산주로서의 상승 가능성을 언급하는 게시글.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['솔리다임', '외인주도', '주주환원']</t>
+          <t>['북한 리스크', '방산주', '김정은']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13510</v>
+        <v>13520</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.27%</t>
+          <t>'+1.35%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G7" t="n">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="H7" t="n">
         <v>2.92</v>
@@ -1070,7 +1070,7 @@
         <v>3.48</v>
       </c>
       <c r="O7" t="n">
-        <v>61573662135</v>
+        <v>62802128330</v>
       </c>
       <c r="P7" t="n">
         <v>31500</v>
@@ -1119,18 +1119,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14590</v>
+        <v>14570</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'+0.28%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F8" t="n">
         <v>39</v>
@@ -1162,7 +1162,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>28039513450</v>
+        <v>28528120490</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8690</v>
+        <v>8700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1254,7 +1254,7 @@
         <v>5.15</v>
       </c>
       <c r="O9" t="n">
-        <v>6661287215</v>
+        <v>6691109545</v>
       </c>
       <c r="P9" t="n">
         <v>15900</v>
@@ -1299,184 +1299,184 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17240</v>
+        <v>213250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.63%</t>
+          <t>'-0.58%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.48</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>494</v>
       </c>
       <c r="G10" t="n">
-        <v>145</v>
+        <v>1685</v>
       </c>
       <c r="H10" t="n">
-        <v>3.77</v>
+        <v>46.13</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17350</v>
+        <v>214500</v>
       </c>
       <c r="K10" t="n">
-        <v>18130</v>
+        <v>206000</v>
       </c>
       <c r="L10" t="n">
-        <v>19070</v>
+        <v>214500</v>
       </c>
       <c r="M10" t="n">
-        <v>16530</v>
+        <v>203500</v>
       </c>
       <c r="N10" t="n">
-        <v>3.29</v>
+        <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>49608946230</v>
+        <v>2461926645500</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-30000</v>
+        <v>-847000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 보안주 폭등과 달리 국내 주가 흐름에 대한 불만이 제기되며, 위꼬리 음봉 패턴을 통한 물량 털어내기 의혹이 제기됨. AI 해킹 이슈와 보안주 상승 기대감이 있으나, 수급 부족 및 주가 조작 가능성에 대한 우려도 나타남.</t>
+          <t>정치적 이슈와 관련된 부정적인 논조와 함께 단기적인 급등을 기대하는 분석이 혼재함. 투자 비중이 높은 투자자의 우려가 드러나며, 시장 교란 가능성에 대한 언급이 있음.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '수급']</t>
+          <t>['정치적 이슈', '급등 기대', '시장 교란']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>213000</v>
+        <v>17120</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.70%</t>
+          <t>'-1.33%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>0.48</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>91</v>
       </c>
       <c r="F11" t="n">
-        <v>496</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>1658</v>
+        <v>145</v>
       </c>
       <c r="H11" t="n">
-        <v>46.13</v>
+        <v>3.77</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>214500</v>
+        <v>17350</v>
       </c>
       <c r="K11" t="n">
-        <v>206000</v>
+        <v>18130</v>
       </c>
       <c r="L11" t="n">
-        <v>214500</v>
+        <v>19070</v>
       </c>
       <c r="M11" t="n">
-        <v>203500</v>
+        <v>16530</v>
       </c>
       <c r="N11" t="n">
-        <v>46.14</v>
+        <v>3.29</v>
       </c>
       <c r="O11" t="n">
-        <v>2429814106500</v>
+        <v>49897333410</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q11" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R11" t="n">
-        <v>-847000</v>
+        <v>-30000</v>
       </c>
       <c r="S11" t="n">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 언급이 주를 이루며, 주가 상승 및 하락에 대한 엇갈린 기대가 혼재. 구체적인 팩트 기반 분석은 부족.</t>
+          <t>미국 보안주 폭등과 달리 국내 주가 흐름에 대한 불만이 제기되며, 위꼬리 음봉 패턴을 통한 물량 털어내기 의혹이 제기됨. AI 해킹 이슈와 보안주 상승 기대감이 있으나, 수급 부족 및 주가 조작 가능성에 대한 우려도 나타남.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['ETF', '레버리지']</t>
+          <t>['보안주', 'AI', '수급']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1498,13 +1498,13 @@
         <v>-0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F12" t="n">
         <v>67</v>
       </c>
       <c r="G12" t="n">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="H12" t="n">
         <v>25.42</v>
@@ -1530,7 +1530,7 @@
         <v>25.47</v>
       </c>
       <c r="O12" t="n">
-        <v>12609711945</v>
+        <v>13023044935</v>
       </c>
       <c r="P12" t="n">
         <v>17950</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>분기 순이익 흑자 전환 및 재무 상태 개선 언급. 목표가 상향 및 배당 기대와 함께 PBR 기반 적정 주가 제시.</t>
+          <t>분기 순이익 흑자 전환 및 재무 상태 개선에 대한 긍정적인 분석과 함께 목표 주가 상향 가능성을 제시함. 과매도권 진입 및 외국인·기관 순매수를 근거로 주가 반등을 기대하는 의견이 있으나, 부정적인 전망도 혼재함.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['순이익', 'PBR', '외인기관']</t>
+          <t>['순이익 흑자전환', '재무 개선', '주가 반등']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16820</v>
+        <v>16830</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.89%</t>
+          <t>'-2.83%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H13" t="n">
         <v>27.89</v>
@@ -1613,7 +1613,7 @@
         <v>16810</v>
       </c>
       <c r="L13" t="n">
-        <v>16850</v>
+        <v>16870</v>
       </c>
       <c r="M13" t="n">
         <v>16450</v>
@@ -1622,7 +1622,7 @@
         <v>27.87</v>
       </c>
       <c r="O13" t="n">
-        <v>31786915395</v>
+        <v>32811007665</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59400</v>
+        <v>59300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.57%</t>
+          <t>'-3.73%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F14" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G14" t="n">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="H14" t="n">
         <v>22.25</v>
@@ -1714,7 +1714,7 @@
         <v>22.26</v>
       </c>
       <c r="O14" t="n">
-        <v>110225627750</v>
+        <v>112102241700</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 언급과 함께 주가 급락 가능성 및 회의적인 전망 제시. 일부 반등 가능성 언급 있으나 근거 부족.</t>
+          <t>정치적 이슈 및 시장 상황에 대한 부정적인 전망이 지배적이며, 두산에너빌리티를 최악의 코스피 종목으로 평가하며 주가 하락에 대한 우려를 표출함. 공매도 물량에 대한 언급과 함께 주가 전망이 매우 비관적임.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '네옴시티', '코스피']</t>
+          <t>['부정적 전망', '공매도', '주가 하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9300</v>
+        <v>9360</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.83%</t>
+          <t>'-7.23%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.19</v>
       </c>
       <c r="E15" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G15" t="n">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="H15" t="n">
         <v>2.5</v>
@@ -1806,7 +1806,7 @@
         <v>3.69</v>
       </c>
       <c r="O15" t="n">
-        <v>47777745190</v>
+        <v>48089338985</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261023_14.xlsx
+++ b/data/trending_integrated_20261023_14.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5300</v>
+        <v>5490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+25.30%</t>
+          <t>'+29.79%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.76</v>
       </c>
       <c r="E2" t="n">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="H2" t="n">
         <v>2.67</v>
@@ -601,7 +601,7 @@
         <v>4355</v>
       </c>
       <c r="L2" t="n">
-        <v>5380</v>
+        <v>5490</v>
       </c>
       <c r="M2" t="n">
         <v>4210</v>
@@ -610,7 +610,7 @@
         <v>3.43</v>
       </c>
       <c r="O2" t="n">
-        <v>17193795714</v>
+        <v>21785285389</v>
       </c>
       <c r="P2" t="n">
         <v>8020</v>
@@ -619,23 +619,23 @@
         <v>3660</v>
       </c>
       <c r="R2" t="n">
-        <v>-112000</v>
+        <v>-66000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>무죄 판결 가능성에 대한 기대와 함께 물량 털어내기에 대한 언급이 있음. 법 전문가들의 의견과 대법원 관련 예상, 그리고 증거재판주의에 대한 논의가 이루어짐.</t>
+          <t>법적 판결 결과에 따른 기대감 표출, 매수세 유입 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['무죄', '대법원', '증거재판주의']</t>
+          <t>['무죄', '증거재판주의']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,7 +643,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1945</v>
+        <v>1896</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.96%</t>
+          <t>'+15.96%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.14</v>
       </c>
       <c r="E3" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="H3" t="n">
         <v>4.87</v>
@@ -702,7 +702,7 @@
         <v>5.01</v>
       </c>
       <c r="O3" t="n">
-        <v>73742327739</v>
+        <v>75699133191</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -711,23 +711,23 @@
         <v>735</v>
       </c>
       <c r="R3" t="n">
-        <v>-2000</v>
+        <v>65000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 관련 사업 성장 기대 및 대기업 수혜주 언급. 단기 급등 후 매도 권유와 물량 확보 움직임 관찰.</t>
+          <t>휴머노이드, 로봇 사업 등 기술적 모멘텀 기반의 상승 기대. 대기업 로봇 사업 수혜 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['휴머노이드', '로봇', 'CES']</t>
+          <t>['로봇주', '휴머노이드', 'CES']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60100</v>
+        <v>59400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+8.48%</t>
+          <t>'+7.22%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.18</v>
       </c>
       <c r="E4" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F4" t="n">
         <v>205</v>
       </c>
       <c r="G4" t="n">
-        <v>1128</v>
+        <v>1135</v>
       </c>
       <c r="H4" t="n">
         <v>38.9</v>
@@ -794,7 +794,7 @@
         <v>37.72</v>
       </c>
       <c r="O4" t="n">
-        <v>657297642450</v>
+        <v>665843213150</v>
       </c>
       <c r="P4" t="n">
         <v>67300</v>
@@ -803,14 +803,14 @@
         <v>23150</v>
       </c>
       <c r="R4" t="n">
-        <v>1522000</v>
+        <v>1712000</v>
       </c>
       <c r="S4" t="n">
-        <v>42000</v>
+        <v>49000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인/기관의 대규모 매수 유입 및 자사주 매입/소각 공시 기반 상승 전망.</t>
+          <t>외인/기관 대규모 매수세 유입 및 자사주 매입/소각 공시 기반의 주가 상승 전망. MSCI 편입 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['자사주', '매입', '공시']</t>
+          <t>['자사주 매입', 'MSCI 편입', '공시']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1260000</v>
+        <v>1254000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.03%</t>
+          <t>'+2.53%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="G5" t="n">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>3246414360500</v>
+        <v>3313613106000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -895,23 +895,23 @@
         <v>468000</v>
       </c>
       <c r="R5" t="n">
-        <v>-405000</v>
+        <v>-414000</v>
       </c>
       <c r="S5" t="n">
-        <v>166000</v>
+        <v>196000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 이슈를 긍정적인 호재로 인식하며, 주가 상승에 대한 기대감이 높게 나타남. 반도체 업황 개선 전망과 함께 바닥 탈출 및 강한 상승 추세 전환을 예상하는 분석이 주를 이룸.</t>
+          <t>솔리다임 상장 철회 호재에 따른 상승 기대감 표출. 기술적 반등 및 주주환원 정책 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['솔리다임 상장 철회', '주가 상승 기대', '반도체 업황']</t>
+          <t>['솔리다임', '주주환원']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3840</v>
+        <v>13540</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.40%</t>
+          <t>'+1.50%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>335</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>172</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>868</v>
+        <v>496</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,91 +963,91 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3750</v>
+        <v>13340</v>
       </c>
       <c r="K6" t="n">
-        <v>3905</v>
+        <v>12840</v>
       </c>
       <c r="L6" t="n">
-        <v>4550</v>
+        <v>13700</v>
       </c>
       <c r="M6" t="n">
-        <v>3815</v>
+        <v>12530</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>154415692119</v>
+        <v>64164262790</v>
       </c>
       <c r="P6" t="n">
-        <v>7050</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>2500</v>
+        <v>1640</v>
       </c>
       <c r="R6" t="n">
-        <v>-251000</v>
+        <v>-140000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크 부각과 함께 방산주로서의 상승 가능성을 언급하는 게시글.</t>
+          <t>유리기판 관련 기술력과 삼성전자 인수합병 가능성에 대한 기대감이 높음. 광섬유 품귀 현상과 외인 매수세 유입에 따른 긍정적 전망이 제시되며, 미국 통신주 하락에도 불구하고 상승 가능성을 주장함.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['북한 리스크', '방산주', '김정은']</t>
+          <t>['유리기판', '인수합병', '광섬유']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13520</v>
+        <v>3780</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.35%</t>
+          <t>'+0.80%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>345</v>
       </c>
       <c r="F7" t="n">
-        <v>62</v>
+        <v>177</v>
       </c>
       <c r="G7" t="n">
-        <v>480</v>
+        <v>876</v>
       </c>
       <c r="H7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13340</v>
+        <v>3750</v>
       </c>
       <c r="K7" t="n">
-        <v>12840</v>
+        <v>3905</v>
       </c>
       <c r="L7" t="n">
-        <v>13700</v>
+        <v>4550</v>
       </c>
       <c r="M7" t="n">
-        <v>12530</v>
+        <v>3755</v>
       </c>
       <c r="N7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>62802128330</v>
+        <v>157358951433</v>
       </c>
       <c r="P7" t="n">
-        <v>31500</v>
+        <v>7050</v>
       </c>
       <c r="Q7" t="n">
-        <v>1640</v>
+        <v>2500</v>
       </c>
       <c r="R7" t="n">
-        <v>-190000</v>
+        <v>-256000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유리기판 관련 기술력과 삼성전자 인수합병 가능성에 대한 기대감이 높음. 광섬유 품귀 현상과 외인 매수세 유입에 따른 긍정적 전망이 제시되며, 미국 통신주 하락에도 불구하고 상승 가능성을 주장함.</t>
+          <t>북한 관련 지정학적 이슈에 따른 방산주 관심 증대. 미국 증시 급등 종목 비교.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유리기판', '인수합병', '광섬유']</t>
+          <t>['북한', '방산주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14570</v>
+        <v>8690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.28%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="H8" t="n">
-        <v>9.890000000000001</v>
+        <v>5.11</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14530</v>
+        <v>8680</v>
       </c>
       <c r="K8" t="n">
-        <v>14190</v>
+        <v>9410</v>
       </c>
       <c r="L8" t="n">
-        <v>14710</v>
+        <v>9460</v>
       </c>
       <c r="M8" t="n">
-        <v>13810</v>
+        <v>8640</v>
       </c>
       <c r="N8" t="n">
-        <v>9.949999999999999</v>
+        <v>5.15</v>
       </c>
       <c r="O8" t="n">
-        <v>28528120490</v>
+        <v>6725649585</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>15900</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>6310</v>
       </c>
       <c r="R8" t="n">
-        <v>-62000</v>
+        <v>-342000</v>
       </c>
       <c r="S8" t="n">
-        <v>69000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>실적 발표 및 주가 조작 관련 의혹 제기가 있으며, 공매도와 대차거래 해지에 대한 주주들의 요청이 혼재.</t>
+          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적', '주가 조작', '공매도']</t>
+          <t>['뇌졸중치료제', '특허', '신약개발']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8700</v>
+        <v>14510</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="H9" t="n">
-        <v>5.11</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8680</v>
+        <v>14530</v>
       </c>
       <c r="K9" t="n">
-        <v>9410</v>
+        <v>14190</v>
       </c>
       <c r="L9" t="n">
-        <v>9460</v>
+        <v>14710</v>
       </c>
       <c r="M9" t="n">
-        <v>8640</v>
+        <v>13810</v>
       </c>
       <c r="N9" t="n">
-        <v>5.15</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>6691109545</v>
+        <v>28891747670</v>
       </c>
       <c r="P9" t="n">
-        <v>15900</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>6310</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-334000</v>
+        <v>-38000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
+          <t>실적 발표 및 주가 조작 관련 의혹 제기가 있으며, 공매도와 대차거래 해지에 대한 주주들의 요청이 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['뇌졸중치료제', '특허', '신약개발']</t>
+          <t>['실적', '주가 조작', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>213250</v>
+        <v>212500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.58%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="G10" t="n">
-        <v>1685</v>
+        <v>1749</v>
       </c>
       <c r="H10" t="n">
         <v>46.13</v>
@@ -1346,7 +1346,7 @@
         <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>2461926645500</v>
+        <v>2505864273250</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1355,14 +1355,14 @@
         <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-847000</v>
+        <v>-819000</v>
       </c>
       <c r="S10" t="n">
-        <v>77000</v>
+        <v>169000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적인 논조와 함께 단기적인 급등을 기대하는 분석이 혼재함. 투자 비중이 높은 투자자의 우려가 드러나며, 시장 교란 가능성에 대한 언급이 있음.</t>
+          <t>정치적 이슈와 관련된 부정적 언급이 다수, 기술적 지표 기반의 상승 기대 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '급등 기대', '시장 교란']</t>
+          <t>['ETF', '기술적 지표']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,184 +1391,184 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17120</v>
+        <v>7120</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.33%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.48</v>
+        <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>145</v>
+        <v>517</v>
       </c>
       <c r="H11" t="n">
-        <v>3.77</v>
+        <v>25.42</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17350</v>
+        <v>7230</v>
       </c>
       <c r="K11" t="n">
-        <v>18130</v>
+        <v>7100</v>
       </c>
       <c r="L11" t="n">
-        <v>19070</v>
+        <v>7220</v>
       </c>
       <c r="M11" t="n">
-        <v>16530</v>
+        <v>7010</v>
       </c>
       <c r="N11" t="n">
-        <v>3.29</v>
+        <v>25.47</v>
       </c>
       <c r="O11" t="n">
-        <v>49897333410</v>
+        <v>13619597755</v>
       </c>
       <c r="P11" t="n">
-        <v>22450</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>6320</v>
+        <v>7010</v>
       </c>
       <c r="R11" t="n">
-        <v>-30000</v>
+        <v>3000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 보안주 폭등과 달리 국내 주가 흐름에 대한 불만이 제기되며, 위꼬리 음봉 패턴을 통한 물량 털어내기 의혹이 제기됨. AI 해킹 이슈와 보안주 상승 기대감이 있으나, 수급 부족 및 주가 조작 가능성에 대한 우려도 나타남.</t>
+          <t>분기 순이익 흑자 전환 및 재무 상태 개선에 대한 긍정적인 분석과 함께 목표 주가 상향 가능성을 제시함. 과매도권 진입 및 외국인·기관 순매수를 근거로 주가 반등을 기대하는 의견이 있으나, 부정적인 전망도 혼재함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '수급']</t>
+          <t>['순이익 흑자전환', '재무 개선', '주가 반등']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7130</v>
+        <v>17030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'-1.84%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.05</v>
+        <v>0.48</v>
       </c>
       <c r="E12" t="n">
-        <v>157</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>512</v>
+        <v>145</v>
       </c>
       <c r="H12" t="n">
-        <v>25.42</v>
+        <v>3.77</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7230</v>
+        <v>17350</v>
       </c>
       <c r="K12" t="n">
-        <v>7100</v>
+        <v>18130</v>
       </c>
       <c r="L12" t="n">
-        <v>7220</v>
+        <v>19070</v>
       </c>
       <c r="M12" t="n">
-        <v>7010</v>
+        <v>16530</v>
       </c>
       <c r="N12" t="n">
-        <v>25.47</v>
+        <v>3.29</v>
       </c>
       <c r="O12" t="n">
-        <v>13023044935</v>
+        <v>50126673410</v>
       </c>
       <c r="P12" t="n">
-        <v>17950</v>
+        <v>22450</v>
       </c>
       <c r="Q12" t="n">
-        <v>7010</v>
+        <v>6320</v>
       </c>
       <c r="R12" t="n">
-        <v>27000</v>
+        <v>-26000</v>
       </c>
       <c r="S12" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>분기 순이익 흑자 전환 및 재무 상태 개선에 대한 긍정적인 분석과 함께 목표 주가 상향 가능성을 제시함. 과매도권 진입 및 외국인·기관 순매수를 근거로 주가 반등을 기대하는 의견이 있으나, 부정적인 전망도 혼재함.</t>
+          <t>미국 보안주 폭등과 달리 국내 주가 흐름에 대한 불만이 제기되며, 위꼬리 음봉 패턴을 통한 물량 털어내기 의혹이 제기됨. AI 해킹 이슈와 보안주 상승 기대감이 있으나, 수급 부족 및 주가 조작 가능성에 대한 우려도 나타남.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['순이익 흑자전환', '재무 개선', '주가 반등']</t>
+          <t>['보안주', 'AI', '수급']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16830</v>
+        <v>16800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.83%</t>
+          <t>'-3.00%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H13" t="n">
         <v>27.89</v>
@@ -1622,7 +1622,7 @@
         <v>27.87</v>
       </c>
       <c r="O13" t="n">
-        <v>32811007665</v>
+        <v>33719376710</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1631,10 +1631,10 @@
         <v>16450</v>
       </c>
       <c r="R13" t="n">
-        <v>119000</v>
+        <v>236000</v>
       </c>
       <c r="S13" t="n">
-        <v>30000</v>
+        <v>34000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59300</v>
+        <v>59100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.73%</t>
+          <t>'-4.06%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F14" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G14" t="n">
-        <v>700</v>
+        <v>730</v>
       </c>
       <c r="H14" t="n">
         <v>22.25</v>
@@ -1714,7 +1714,7 @@
         <v>22.26</v>
       </c>
       <c r="O14" t="n">
-        <v>112102241700</v>
+        <v>116893221950</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1723,23 +1723,23 @@
         <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-203000</v>
+        <v>-248000</v>
       </c>
       <c r="S14" t="n">
-        <v>-124000</v>
+        <v>-143000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 시장 상황에 대한 부정적인 전망이 지배적이며, 두산에너빌리티를 최악의 코스피 종목으로 평가하며 주가 하락에 대한 우려를 표출함. 공매도 물량에 대한 언급과 함께 주가 전망이 매우 비관적임.</t>
+          <t>정치적 이슈 및 미국 증시 폭락에 따른 부정적 전망, 공매도 물량 부담 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['부정적 전망', '공매도', '주가 하락']</t>
+          <t>['미국 증시', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9360</v>
+        <v>9240</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-7.23%</t>
+          <t>'-8.42%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.19</v>
       </c>
       <c r="E15" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G15" t="n">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H15" t="n">
         <v>2.5</v>
@@ -1806,7 +1806,7 @@
         <v>3.69</v>
       </c>
       <c r="O15" t="n">
-        <v>48089338985</v>
+        <v>48616998480</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1815,10 +1815,10 @@
         <v>2270</v>
       </c>
       <c r="R15" t="n">
-        <v>13000</v>
+        <v>-31000</v>
       </c>
       <c r="S15" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261023_14.xlsx
+++ b/data/trending_integrated_20261023_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.76</v>
       </c>
       <c r="E2" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G2" t="n">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="H2" t="n">
         <v>2.67</v>
@@ -610,7 +610,7 @@
         <v>3.43</v>
       </c>
       <c r="O2" t="n">
-        <v>21785285389</v>
+        <v>22006625719</v>
       </c>
       <c r="P2" t="n">
         <v>8020</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>법적 판결 결과에 따른 기대감 표출, 매수세 유입 언급.</t>
+          <t>주요 인물의 무죄 판결 기대감과 함께 높은 변동성을 보이며, 일부 투자자들은 큰 폭의 상승을 예상하고 있습니다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['무죄', '증거재판주의']</t>
+          <t>['무죄', '텐버거', '상승']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1896</v>
+        <v>1866</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.96%</t>
+          <t>'+14.13%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.14</v>
       </c>
       <c r="E3" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="F3" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H3" t="n">
         <v>4.87</v>
@@ -702,7 +702,7 @@
         <v>5.01</v>
       </c>
       <c r="O3" t="n">
-        <v>75699133191</v>
+        <v>77128796750</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59400</v>
+        <v>59000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.22%</t>
+          <t>'+6.50%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.18</v>
       </c>
       <c r="E4" t="n">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="F4" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G4" t="n">
-        <v>1135</v>
+        <v>1167</v>
       </c>
       <c r="H4" t="n">
         <v>38.9</v>
@@ -794,7 +794,7 @@
         <v>37.72</v>
       </c>
       <c r="O4" t="n">
-        <v>665843213150</v>
+        <v>699835392850</v>
       </c>
       <c r="P4" t="n">
         <v>67300</v>
@@ -803,7 +803,7 @@
         <v>23150</v>
       </c>
       <c r="R4" t="n">
-        <v>1712000</v>
+        <v>1771000</v>
       </c>
       <c r="S4" t="n">
         <v>49000</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1254000</v>
+        <v>1267000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.53%</t>
+          <t>'+3.60%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="G5" t="n">
-        <v>1550</v>
+        <v>1626</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -877,7 +877,7 @@
         <v>1200000</v>
       </c>
       <c r="L5" t="n">
-        <v>1263000</v>
+        <v>1268000</v>
       </c>
       <c r="M5" t="n">
         <v>1171000</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>3313613106000</v>
+        <v>3428134880500</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -895,23 +895,23 @@
         <v>468000</v>
       </c>
       <c r="R5" t="n">
-        <v>-414000</v>
+        <v>-419000</v>
       </c>
       <c r="S5" t="n">
         <v>196000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 호재에 따른 상승 기대감 표출. 기술적 반등 및 주주환원 정책 언급.</t>
+          <t>솔리다임 상장 철회 이슈를 호재로 인식하며, 반도체 섹터 전반의 상승 가능성과 주주 환원 정책에 대한 기대감이 나타나고 있습니다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['솔리다임', '주주환원']</t>
+          <t>['솔리다임', '상장 철회', '주주 환원']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -952,7 +952,7 @@
         <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>64164262790</v>
+        <v>65056526415</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3780</v>
+        <v>14550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.80%</t>
+          <t>'+0.14%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>345</v>
+        <v>128</v>
       </c>
       <c r="F7" t="n">
-        <v>177</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>876</v>
+        <v>204</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3750</v>
+        <v>14530</v>
       </c>
       <c r="K7" t="n">
-        <v>3905</v>
+        <v>14190</v>
       </c>
       <c r="L7" t="n">
-        <v>4550</v>
+        <v>14710</v>
       </c>
       <c r="M7" t="n">
-        <v>3755</v>
+        <v>13810</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>157358951433</v>
+        <v>29831584395</v>
       </c>
       <c r="P7" t="n">
-        <v>7050</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>2500</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-256000</v>
+        <v>-36000</v>
       </c>
       <c r="S7" t="n">
-        <v>-25000</v>
+        <v>71000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 이슈에 따른 방산주 관심 증대. 미국 증시 급등 종목 비교.</t>
+          <t>주가 조작 및 공매도 이슈에 대한 불만이 제기되며, 실적 발표와 대차 해지 신청 참여 독려 등 부정적인 의견이 일부 관찰됩니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['북한', '방산주']</t>
+          <t>['주가 조작', '공매도', '실적']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H8" t="n">
         <v>5.11</v>
@@ -1162,7 +1162,7 @@
         <v>5.15</v>
       </c>
       <c r="O8" t="n">
-        <v>6725649585</v>
+        <v>6802182325</v>
       </c>
       <c r="P8" t="n">
         <v>15900</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14510</v>
+        <v>214000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.14%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>124</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>496</v>
       </c>
       <c r="G9" t="n">
-        <v>199</v>
+        <v>1770</v>
       </c>
       <c r="H9" t="n">
-        <v>9.890000000000001</v>
+        <v>46.13</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14530</v>
+        <v>214500</v>
       </c>
       <c r="K9" t="n">
-        <v>14190</v>
+        <v>206000</v>
       </c>
       <c r="L9" t="n">
-        <v>14710</v>
+        <v>214500</v>
       </c>
       <c r="M9" t="n">
-        <v>13810</v>
+        <v>203500</v>
       </c>
       <c r="N9" t="n">
-        <v>9.949999999999999</v>
+        <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>28891747670</v>
+        <v>2598676122250</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-38000</v>
+        <v>-837000</v>
       </c>
       <c r="S9" t="n">
-        <v>71000</v>
+        <v>169000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>실적 발표 및 주가 조작 관련 의혹 제기가 있으며, 공매도와 대차거래 해지에 대한 주주들의 요청이 혼재.</t>
+          <t>정치적 이슈와 함께 투자 심리가 혼재된 가운데, 일부 투자자들은 반도체 섹터 전망을 근거로 상승을 기대하고 있습니다.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['실적', '주가 조작', '공매도']</t>
+          <t>['반도체', 'ETF', '추세']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,18 +1292,18 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>212500</v>
+        <v>3715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1311,71 +1311,71 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>373</v>
       </c>
       <c r="F10" t="n">
-        <v>491</v>
+        <v>188</v>
       </c>
       <c r="G10" t="n">
-        <v>1749</v>
+        <v>978</v>
       </c>
       <c r="H10" t="n">
-        <v>46.13</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>214500</v>
+        <v>3750</v>
       </c>
       <c r="K10" t="n">
-        <v>206000</v>
+        <v>3905</v>
       </c>
       <c r="L10" t="n">
-        <v>214500</v>
+        <v>4550</v>
       </c>
       <c r="M10" t="n">
-        <v>203500</v>
+        <v>3685</v>
       </c>
       <c r="N10" t="n">
-        <v>46.14</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2505864273250</v>
+        <v>160373791162</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>7050</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>2500</v>
       </c>
       <c r="R10" t="n">
-        <v>-819000</v>
+        <v>-256000</v>
       </c>
       <c r="S10" t="n">
-        <v>169000</v>
+        <v>-25000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적 언급이 다수, 기술적 지표 기반의 상승 기대 언급.</t>
+          <t>북한 관련 이슈와 미 증시 변동성에 따른 방산주에 대한 관심이 높아지고 있으며, 일부 투자자들은 급등을 예상하고 있습니다.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['ETF', '기술적 지표']</t>
+          <t>['북한', '방산주', '미 증시']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7120</v>
+        <v>7110</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-1.66%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G11" t="n">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="H11" t="n">
         <v>25.42</v>
@@ -1438,7 +1438,7 @@
         <v>25.47</v>
       </c>
       <c r="O11" t="n">
-        <v>13619597755</v>
+        <v>14313122990</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1447,7 +1447,7 @@
         <v>7010</v>
       </c>
       <c r="R11" t="n">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="S11" t="n">
         <v>-3000</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17030</v>
+        <v>16990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.84%</t>
+          <t>'-2.07%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.48</v>
       </c>
       <c r="E12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H12" t="n">
         <v>3.77</v>
@@ -1530,7 +1530,7 @@
         <v>3.29</v>
       </c>
       <c r="O12" t="n">
-        <v>50126673410</v>
+        <v>50449762610</v>
       </c>
       <c r="P12" t="n">
         <v>22450</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16800</v>
+        <v>16850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.00%</t>
+          <t>'-2.71%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F13" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H13" t="n">
         <v>27.89</v>
@@ -1622,7 +1622,7 @@
         <v>27.87</v>
       </c>
       <c r="O13" t="n">
-        <v>33719376710</v>
+        <v>34632128400</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1631,7 +1631,7 @@
         <v>16450</v>
       </c>
       <c r="R13" t="n">
-        <v>236000</v>
+        <v>238000</v>
       </c>
       <c r="S13" t="n">
         <v>34000</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59100</v>
+        <v>59200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.06%</t>
+          <t>'-3.90%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F14" t="n">
         <v>171</v>
       </c>
       <c r="G14" t="n">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="H14" t="n">
         <v>22.25</v>
@@ -1714,7 +1714,7 @@
         <v>22.26</v>
       </c>
       <c r="O14" t="n">
-        <v>116893221950</v>
+        <v>120376184950</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1723,7 +1723,7 @@
         <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-248000</v>
+        <v>-256000</v>
       </c>
       <c r="S14" t="n">
         <v>-143000</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9240</v>
+        <v>9280</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.42%</t>
+          <t>'-8.03%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.19</v>
       </c>
       <c r="E15" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F15" t="n">
         <v>74</v>
       </c>
       <c r="G15" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H15" t="n">
         <v>2.5</v>
@@ -1806,7 +1806,7 @@
         <v>3.69</v>
       </c>
       <c r="O15" t="n">
-        <v>48616998480</v>
+        <v>49115833515</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 부정적 전망이 지배적이며, 조정 및 횡보 가능성이 언급되고 일부에서는 매도 신호 포착.</t>
+          <t>급락 이후 조정 및 횡보를 예상하는 의견이 다수이며, 일부 투자자들은 단기적인 하락 가능성과 매도 시점을 논하고 있습니다.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 하락', '조정', '매도 신호']</t>
+          <t>['급락', '횡보', '매도']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261023_14.xlsx
+++ b/data/trending_integrated_20261023_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.76</v>
       </c>
       <c r="E2" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G2" t="n">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="H2" t="n">
         <v>2.67</v>
@@ -610,7 +610,7 @@
         <v>3.43</v>
       </c>
       <c r="O2" t="n">
-        <v>22006625719</v>
+        <v>22079362729</v>
       </c>
       <c r="P2" t="n">
         <v>8020</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>주요 인물의 무죄 판결 기대감과 함께 높은 변동성을 보이며, 일부 투자자들은 큰 폭의 상승을 예상하고 있습니다.</t>
+          <t>오세훈 전 시장 관련 무죄 판결에 대한 언급이 많으며, 이를 기반으로 '텐버거', '10연상' 등의 기대감이 형성됨. 다만, 실제 주가 상승으로 이어질 구체적인 팩트는 부족함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['무죄', '텐버거', '상승']</t>
+          <t>['무죄', '대권', '차기 대통령']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1866</v>
+        <v>1869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.13%</t>
+          <t>'+14.31%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="H3" t="n">
         <v>4.87</v>
@@ -702,7 +702,7 @@
         <v>5.01</v>
       </c>
       <c r="O3" t="n">
-        <v>77128796750</v>
+        <v>77969720631</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드, 로봇 사업 등 기술적 모멘텀 기반의 상승 기대. 대기업 로봇 사업 수혜 전망.</t>
+          <t>휴머노이드, 배터리 충전 상용화 등 긍정적인 기술 언급이 있으나, 주가 하락 및 '털어라', '튀세요'와 같은 부정적 전망이 지배적임. 외인 매수세가 언급되었으나 명확한 근거는 부족함.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇주', '휴머노이드', 'CES']</t>
+          <t>['휴머노이드', '로봇주', '배터리']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59000</v>
+        <v>59200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.50%</t>
+          <t>'+6.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.18</v>
       </c>
       <c r="E4" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G4" t="n">
-        <v>1167</v>
+        <v>1176</v>
       </c>
       <c r="H4" t="n">
         <v>38.9</v>
@@ -794,7 +794,7 @@
         <v>37.72</v>
       </c>
       <c r="O4" t="n">
-        <v>699835392850</v>
+        <v>710410993850</v>
       </c>
       <c r="P4" t="n">
         <v>67300</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1267000</v>
+        <v>1272000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+3.60%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="G5" t="n">
-        <v>1626</v>
+        <v>1770</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -877,7 +877,7 @@
         <v>1200000</v>
       </c>
       <c r="L5" t="n">
-        <v>1268000</v>
+        <v>1272000</v>
       </c>
       <c r="M5" t="n">
         <v>1171000</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>3428134880500</v>
+        <v>3590863945000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 이슈를 호재로 인식하며, 반도체 섹터 전반의 상승 가능성과 주주 환원 정책에 대한 기대감이 나타나고 있습니다.</t>
+          <t>솔리다임 상장 철회 발표와 특별배당 관련 언급이 있으나, 주가 상승에 대한 기대감이 더 큰 비중을 차지함. 28일 주주환원 정책 발표가 예정되어 있어 팩트 기반 분석 가능성이 있음.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['솔리다임', '상장 철회', '주주 환원']</t>
+          <t>['특별배당', '주주환원', '상장철회']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13540</v>
+        <v>13640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.50%</t>
+          <t>'+2.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G6" t="n">
-        <v>514</v>
+        <v>537</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>65056526415</v>
+        <v>67419253825</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14550</v>
+        <v>3790</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.14%</t>
+          <t>'+1.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>128</v>
+        <v>388</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>193</v>
       </c>
       <c r="G7" t="n">
-        <v>204</v>
+        <v>1020</v>
       </c>
       <c r="H7" t="n">
-        <v>9.890000000000001</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14530</v>
+        <v>3750</v>
       </c>
       <c r="K7" t="n">
-        <v>14190</v>
+        <v>3905</v>
       </c>
       <c r="L7" t="n">
-        <v>14710</v>
+        <v>4550</v>
       </c>
       <c r="M7" t="n">
-        <v>13810</v>
+        <v>3685</v>
       </c>
       <c r="N7" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>29831584395</v>
+        <v>162642141853</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>7050</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>2500</v>
       </c>
       <c r="R7" t="n">
-        <v>-36000</v>
+        <v>-256000</v>
       </c>
       <c r="S7" t="n">
-        <v>71000</v>
+        <v>-25000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 이슈에 대한 불만이 제기되며, 실적 발표와 대차 해지 신청 참여 독려 등 부정적인 의견이 일부 관찰됩니다.</t>
+          <t>북한 관련 이슈와 미 증시 변동성에 따른 방산주에 대한 관심이 높아지고 있으며, 일부 투자자들은 급등을 예상하고 있습니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '실적']</t>
+          <t>['북한', '방산주', '미 증시']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8690</v>
+        <v>14630</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.69%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H8" t="n">
-        <v>5.11</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,91 +1147,91 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>8680</v>
+        <v>14530</v>
       </c>
       <c r="K8" t="n">
-        <v>9410</v>
+        <v>14190</v>
       </c>
       <c r="L8" t="n">
-        <v>9460</v>
+        <v>14710</v>
       </c>
       <c r="M8" t="n">
-        <v>8640</v>
+        <v>13810</v>
       </c>
       <c r="N8" t="n">
-        <v>5.15</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>6802182325</v>
+        <v>30461966235</v>
       </c>
       <c r="P8" t="n">
-        <v>15900</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>6310</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>-342000</v>
+        <v>-36000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
+          <t>주가 조작 및 공매도 이슈에 대한 불만이 제기되며, 실적 발표와 대차 해지 신청 참여 독려 등 부정적인 의견이 일부 관찰됩니다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['뇌졸중치료제', '특허', '신약개발']</t>
+          <t>['주가 조작', '공매도', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>214000</v>
+        <v>8700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.23%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>109</v>
       </c>
       <c r="F9" t="n">
-        <v>496</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>1770</v>
+        <v>214</v>
       </c>
       <c r="H9" t="n">
-        <v>46.13</v>
+        <v>5.11</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,130 +1239,130 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>214500</v>
+        <v>8680</v>
       </c>
       <c r="K9" t="n">
-        <v>206000</v>
+        <v>9410</v>
       </c>
       <c r="L9" t="n">
-        <v>214500</v>
+        <v>9460</v>
       </c>
       <c r="M9" t="n">
-        <v>203500</v>
+        <v>8640</v>
       </c>
       <c r="N9" t="n">
-        <v>46.14</v>
+        <v>5.15</v>
       </c>
       <c r="O9" t="n">
-        <v>2598676122250</v>
+        <v>6837885295</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>15900</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>6310</v>
       </c>
       <c r="R9" t="n">
-        <v>-837000</v>
+        <v>-342000</v>
       </c>
       <c r="S9" t="n">
-        <v>169000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 투자 심리가 혼재된 가운데, 일부 투자자들은 반도체 섹터 전망을 근거로 상승을 기대하고 있습니다.</t>
+          <t>뇌졸중 치료제 관련 특허 보유 및 3상 성공 가능성 언급. 신약 개발 외자 유치 및 합병 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', 'ETF', '추세']</t>
+          <t>['뇌졸중치료제', '특허', '신약개발']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3715</v>
+        <v>214750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.93%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>373</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>188</v>
+        <v>494</v>
       </c>
       <c r="G10" t="n">
-        <v>978</v>
+        <v>1700</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>46.13</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3750</v>
+        <v>214500</v>
       </c>
       <c r="K10" t="n">
-        <v>3905</v>
+        <v>206000</v>
       </c>
       <c r="L10" t="n">
-        <v>4550</v>
+        <v>215000</v>
       </c>
       <c r="M10" t="n">
-        <v>3685</v>
+        <v>203500</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>160373791162</v>
+        <v>2677516850500</v>
       </c>
       <c r="P10" t="n">
-        <v>7050</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>2500</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-256000</v>
+        <v>-837000</v>
       </c>
       <c r="S10" t="n">
-        <v>-25000</v>
+        <v>169000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>북한 관련 이슈와 미 증시 변동성에 따른 방산주에 대한 관심이 높아지고 있으며, 일부 투자자들은 급등을 예상하고 있습니다.</t>
+          <t>향후 22만, 24만원 상승 및 10% 이상 상승 가능성이 언급되었으나, 구체적인 공시나 뉴스 기반 근거는 부족함. 20, 60, 120일선이 살아있는 추세는 긍정적으로 평가됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['북한', '방산주', '미 증시']</t>
+          <t>['추세', 'ETF', '반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7110</v>
+        <v>7120</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.66%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F11" t="n">
         <v>68</v>
       </c>
       <c r="G11" t="n">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="H11" t="n">
         <v>25.42</v>
@@ -1438,7 +1438,7 @@
         <v>25.47</v>
       </c>
       <c r="O11" t="n">
-        <v>14313122990</v>
+        <v>14572648665</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16990</v>
+        <v>17070</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.07%</t>
+          <t>'-1.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.48</v>
       </c>
       <c r="E12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F12" t="n">
         <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="H12" t="n">
         <v>3.77</v>
@@ -1530,7 +1530,7 @@
         <v>3.29</v>
       </c>
       <c r="O12" t="n">
-        <v>50449762610</v>
+        <v>50661398940</v>
       </c>
       <c r="P12" t="n">
         <v>22450</v>
@@ -1579,18 +1579,18 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16850</v>
+        <v>16870</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.71%</t>
+          <t>'-2.60%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F13" t="n">
         <v>73</v>
@@ -1613,7 +1613,7 @@
         <v>16810</v>
       </c>
       <c r="L13" t="n">
-        <v>16870</v>
+        <v>16890</v>
       </c>
       <c r="M13" t="n">
         <v>16450</v>
@@ -1622,7 +1622,7 @@
         <v>27.87</v>
       </c>
       <c r="O13" t="n">
-        <v>34632128400</v>
+        <v>35762382910</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59200</v>
+        <v>59400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.90%</t>
+          <t>'-3.57%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>278</v>
       </c>
       <c r="F14" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G14" t="n">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="H14" t="n">
         <v>22.25</v>
@@ -1714,7 +1714,7 @@
         <v>22.26</v>
       </c>
       <c r="O14" t="n">
-        <v>120376184950</v>
+        <v>129833132250</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9280</v>
+        <v>9240</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.03%</t>
+          <t>'-8.42%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.19</v>
       </c>
       <c r="E15" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F15" t="n">
         <v>74</v>
       </c>
       <c r="G15" t="n">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="H15" t="n">
         <v>2.5</v>
@@ -1806,7 +1806,7 @@
         <v>3.69</v>
       </c>
       <c r="O15" t="n">
-        <v>49115833515</v>
+        <v>49705984845</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>급락 이후 조정 및 횡보를 예상하는 의견이 다수이며, 일부 투자자들은 단기적인 하락 가능성과 매도 시점을 논하고 있습니다.</t>
+          <t>AI 산업통상부 장관 표창 및 북미·유럽 수출 관련 뉴스가 있으나, 주가 하락에 대한 우려와 '끝났다', '조정 및 횡보 예상' 등의 부정적인 전망이 주를 이룸. 20% 급락 이후 하한가 출발 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['급락', '횡보', '매도']</t>
+          <t>['AI', '수출', '주가 하락']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261023_14.xlsx
+++ b/data/trending_integrated_20261023_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.76</v>
       </c>
       <c r="E2" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F2" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G2" t="n">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="H2" t="n">
         <v>2.67</v>
@@ -610,7 +610,7 @@
         <v>3.43</v>
       </c>
       <c r="O2" t="n">
-        <v>22079362729</v>
+        <v>22260011179</v>
       </c>
       <c r="P2" t="n">
         <v>8020</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>오세훈 전 시장 관련 무죄 판결에 대한 언급이 많으며, 이를 기반으로 '텐버거', '10연상' 등의 기대감이 형성됨. 다만, 실제 주가 상승으로 이어질 구체적인 팩트는 부족함.</t>
+          <t>정치인 관련 이슈에 따른 급등세를 보였으며, 향후 큰 상승에 대한 기대감이 높으나, 근거 없는 기대에 치우친 경향이 있음.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['무죄', '대권', '차기 대통령']</t>
+          <t>['정치 이슈', '급등 기대']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.31%</t>
+          <t>'+14.25%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.14</v>
       </c>
       <c r="E3" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H3" t="n">
         <v>4.87</v>
@@ -702,7 +702,7 @@
         <v>5.01</v>
       </c>
       <c r="O3" t="n">
-        <v>77969720631</v>
+        <v>78612412883</v>
       </c>
       <c r="P3" t="n">
         <v>4980</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>휴머노이드, 배터리 충전 상용화 등 긍정적인 기술 언급이 있으나, 주가 하락 및 '털어라', '튀세요'와 같은 부정적 전망이 지배적임. 외인 매수세가 언급되었으나 명확한 근거는 부족함.</t>
+          <t>주가 하락 추세가 지속되며 탈출 및 저점 매수 기회에 대한 언급이 많고, 로봇 관련 기대감도 있으나, 전반적으로 부정적인 전망이 우세함.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['휴머노이드', '로봇주', '배터리']</t>
+          <t>['주가 하락', '저점 매수', '로봇주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59200</v>
+        <v>59400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+6.86%</t>
+          <t>'+7.22%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1.18</v>
       </c>
       <c r="E4" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F4" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G4" t="n">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="H4" t="n">
         <v>38.9</v>
@@ -794,7 +794,7 @@
         <v>37.72</v>
       </c>
       <c r="O4" t="n">
-        <v>710410993850</v>
+        <v>720137691750</v>
       </c>
       <c r="P4" t="n">
         <v>67300</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1272000</v>
+        <v>1266000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.01%</t>
+          <t>'+3.52%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G5" t="n">
-        <v>1770</v>
+        <v>1785</v>
       </c>
       <c r="H5" t="n">
         <v>48.77</v>
@@ -877,7 +877,7 @@
         <v>1200000</v>
       </c>
       <c r="L5" t="n">
-        <v>1272000</v>
+        <v>1275000</v>
       </c>
       <c r="M5" t="n">
         <v>1171000</v>
@@ -886,7 +886,7 @@
         <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>3590863945000</v>
+        <v>3695674584000</v>
       </c>
       <c r="P5" t="n">
         <v>2987000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>솔리다임 상장 철회 발표와 특별배당 관련 언급이 있으나, 주가 상승에 대한 기대감이 더 큰 비중을 차지함. 28일 주주환원 정책 발표가 예정되어 있어 팩트 기반 분석 가능성이 있음.</t>
+          <t>솔리다임 상장 철회 이슈로 인한 긍정적 반응과 함께 추가적인 주주환원 기대감이 있으나, 전반적인 시장 움직임에 대한 언급이 주를 이룸.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['특별배당', '주주환원', '상장철회']</t>
+          <t>['솔리다임', '주주환원', '호재']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13640</v>
+        <v>13800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.25%</t>
+          <t>'+3.45%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F6" t="n">
         <v>63</v>
       </c>
       <c r="G6" t="n">
-        <v>537</v>
+        <v>588</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -969,7 +969,7 @@
         <v>12840</v>
       </c>
       <c r="L6" t="n">
-        <v>13700</v>
+        <v>13880</v>
       </c>
       <c r="M6" t="n">
         <v>12530</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>67419253825</v>
+        <v>70684603245</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3790</v>
+        <v>3815</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.07%</t>
+          <t>'+1.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F7" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G7" t="n">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>162642141853</v>
+        <v>164015173224</v>
       </c>
       <c r="P7" t="n">
         <v>7050</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14630</v>
+        <v>14680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.69%</t>
+          <t>'+1.03%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F8" t="n">
         <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H8" t="n">
         <v>9.890000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>30461966235</v>
+        <v>31420139355</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>주가 조작 및 공매도 이슈에 대한 불만이 제기되며, 실적 발표와 대차 해지 신청 참여 독려 등 부정적인 의견이 일부 관찰됩니다.</t>
+          <t>정치적 이슈 및 공매도 관련 부정적 언급이 많으며, 주가 하락에 대한 우려가 있으나, 긍정적 소식 및 거래량 증가를 통한 상승 기대를 일부 언급함.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '실적']</t>
+          <t>['공매도', '주가 하락', '거래량']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8700</v>
+        <v>8690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H9" t="n">
         <v>5.11</v>
@@ -1254,7 +1254,7 @@
         <v>5.15</v>
       </c>
       <c r="O9" t="n">
-        <v>6837885295</v>
+        <v>6891748815</v>
       </c>
       <c r="P9" t="n">
         <v>15900</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>214750</v>
+        <v>214000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="G10" t="n">
-        <v>1700</v>
+        <v>1726</v>
       </c>
       <c r="H10" t="n">
         <v>46.13</v>
@@ -1346,7 +1346,7 @@
         <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>2677516850500</v>
+        <v>2750406275000</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>향후 22만, 24만원 상승 및 10% 이상 상승 가능성이 언급되었으나, 구체적인 공시나 뉴스 기반 근거는 부족함. 20, 60, 120일선이 살아있는 추세는 긍정적으로 평가됨.</t>
+          <t>정치 관련 언급이 많고, 일부 투자자들의 긍정적 기대감 및 기술적 지표 언급이 있으나, 구체적인 호재나 악재 분석은 부족함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['추세', 'ETF', '반도체']</t>
+          <t>['기술적 지표', '투자자 기대']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7120</v>
+        <v>7110</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-1.66%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F11" t="n">
         <v>68</v>
       </c>
       <c r="G11" t="n">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="H11" t="n">
         <v>25.42</v>
@@ -1438,7 +1438,7 @@
         <v>25.47</v>
       </c>
       <c r="O11" t="n">
-        <v>14572648665</v>
+        <v>14984451170</v>
       </c>
       <c r="P11" t="n">
         <v>17950</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>분기 순이익 흑자 전환 및 재무 상태 개선에 대한 긍정적인 분석과 함께 목표 주가 상향 가능성을 제시함. 과매도권 진입 및 외국인·기관 순매수를 근거로 주가 반등을 기대하는 의견이 있으나, 부정적인 전망도 혼재함.</t>
+          <t>3분기 호실적 및 재무 상태 개선, 과매도 구간 진입에 따른 반등 가능성에 대한 긍정적 분석과 함께, 목표가 하향 및 부채 관련 부정적 전망이 혼재함.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['순이익 흑자전환', '재무 개선', '주가 반등']</t>
+          <t>['3분기 실적', '재무 개선', '반등 가능성']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17070</v>
+        <v>16980</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.61%</t>
+          <t>'-2.13%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.48</v>
       </c>
       <c r="E12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
         <v>143</v>
@@ -1530,7 +1530,7 @@
         <v>3.29</v>
       </c>
       <c r="O12" t="n">
-        <v>50661398940</v>
+        <v>50949581310</v>
       </c>
       <c r="P12" t="n">
         <v>22450</v>
@@ -1579,18 +1579,18 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16870</v>
+        <v>16860</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.60%</t>
+          <t>'-2.66%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F13" t="n">
         <v>73</v>
@@ -1613,7 +1613,7 @@
         <v>16810</v>
       </c>
       <c r="L13" t="n">
-        <v>16890</v>
+        <v>16900</v>
       </c>
       <c r="M13" t="n">
         <v>16450</v>
@@ -1622,7 +1622,7 @@
         <v>27.87</v>
       </c>
       <c r="O13" t="n">
-        <v>35762382910</v>
+        <v>36969596845</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59400</v>
+        <v>59300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.57%</t>
+          <t>'-3.73%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F14" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G14" t="n">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="H14" t="n">
         <v>22.25</v>
@@ -1714,7 +1714,7 @@
         <v>22.26</v>
       </c>
       <c r="O14" t="n">
-        <v>129833132250</v>
+        <v>133216381100</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 미국 증시 폭락에 따른 부정적 전망, 공매도 물량 부담 언급.</t>
+          <t>정치적 언급과 함께 주가 하락에 대한 부정적 전망이 지배적이며, 일부에서는 공매도 물량에 대한 언급이 있으나, 구체적인 분석은 부족함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['미국 증시', '공매도']</t>
+          <t>['정치적 언급', '공매도', '주가 하락']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9240</v>
+        <v>9270</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-8.42%</t>
+          <t>'-8.13%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-1.19</v>
       </c>
       <c r="E15" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="H15" t="n">
         <v>2.5</v>
@@ -1806,7 +1806,7 @@
         <v>3.69</v>
       </c>
       <c r="O15" t="n">
-        <v>49705984845</v>
+        <v>50162855265</v>
       </c>
       <c r="P15" t="n">
         <v>11690</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 산업통상부 장관 표창 및 북미·유럽 수출 관련 뉴스가 있으나, 주가 하락에 대한 우려와 '끝났다', '조정 및 횡보 예상' 등의 부정적인 전망이 주를 이룸. 20% 급락 이후 하한가 출발 가능성 언급.</t>
+          <t>주가 급락 이후 조정 및 횡보를 예상하는 의견이 많으며, 일부에서는 시장 상황에 대한 부정적 언급과 함께 투매 및 하한가 가능성을 제기함.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '수출', '주가 하락']</t>
+          <t>['주가 급락', '조정 예상', '투매']</t>
         </is>
       </c>
       <c r="X15" t="n">
